--- a/Diary/凯哥高数复习规划.xlsx
+++ b/Diary/凯哥高数复习规划.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C751FEE-EB5F-4A87-ADE9-F22071E15EAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD51CA60-870A-45F5-AE0E-1DD41D8ECA3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
   <si>
     <t>日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -279,15 +279,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>分部积分法</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>有理函数积分、三角有理函数积分</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>换元法例题</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -306,6 +298,69 @@
     <t>上册专题
 6-1
 6-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>换元法例题（题型二）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分部积分法（题型三）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>定积分的几何意义
+定积分的定义
+牛顿莱布尼兹公式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>定积分的基本计算方法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>变上限积分函数
+积分中值定理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上册专题
+7-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>定积分的基本计算</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>利用定积分定义求极限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>变限积分函数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上册专题
+7-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>微分法的思想概述</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>定积分的几何应用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>定积分的几何应用例题</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上册专题
+8-1
+8-2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -410,14 +465,7 @@
   </cellStyleXfs>
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -426,26 +474,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -727,7 +784,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C2:I63"/>
+  <dimension ref="C8:I179"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="42.21875" customWidth="1"/>
@@ -736,769 +793,1848 @@
     <col min="9" max="9" width="15.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="H2" s="1"/>
-    </row>
     <row r="8" spans="3:9" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
     </row>
     <row r="9" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="I9" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="10" spans="3:9" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="C10" s="3">
+      <c r="C10" s="1">
         <v>1</v>
       </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="11" t="s">
+      <c r="D10" s="1"/>
+      <c r="E10" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
     </row>
     <row r="11" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C11" s="3">
+      <c r="C11" s="1">
         <v>2</v>
       </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="3" t="s">
+      <c r="D11" s="1"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
     </row>
     <row r="12" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C12" s="3">
+      <c r="C12" s="1">
         <v>3</v>
       </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="3" t="s">
+      <c r="D12" s="1"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
     </row>
     <row r="13" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C13" s="3">
+      <c r="C13" s="1">
         <v>4</v>
       </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="3" t="s">
+      <c r="D13" s="1"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
     </row>
     <row r="14" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C14" s="3">
+      <c r="C14" s="1">
         <v>5</v>
       </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="3" t="s">
+      <c r="D14" s="1"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
     </row>
     <row r="15" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C15" s="3">
+      <c r="C15" s="1">
         <v>6</v>
       </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="3" t="s">
+      <c r="D15" s="1"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
     </row>
     <row r="16" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C16" s="3">
+      <c r="C16" s="1">
         <v>7</v>
       </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="3" t="s">
+      <c r="D16" s="1"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
     </row>
     <row r="17" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C17" s="3">
+      <c r="C17" s="1">
         <v>8</v>
       </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="11" t="s">
+      <c r="D17" s="1"/>
+      <c r="E17" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
     </row>
     <row r="18" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C18" s="3">
+      <c r="C18" s="1">
         <v>9</v>
       </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="3" t="s">
+      <c r="D18" s="1"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
     </row>
     <row r="19" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C19" s="3">
+      <c r="C19" s="1">
         <v>10</v>
       </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="3" t="s">
+      <c r="D19" s="1"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
     </row>
     <row r="20" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C20" s="3">
+      <c r="C20" s="1">
         <v>11</v>
       </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="3" t="s">
+      <c r="D20" s="1"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
     </row>
     <row r="21" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C21" s="3">
+      <c r="C21" s="1">
         <v>12</v>
       </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="3" t="s">
+      <c r="D21" s="1"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
     </row>
     <row r="22" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C22" s="3">
+      <c r="C22" s="1">
         <v>13</v>
       </c>
-      <c r="D22" s="3"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="3" t="s">
+      <c r="D22" s="1"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
     </row>
     <row r="23" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C23" s="3">
+      <c r="C23" s="1">
         <v>14</v>
       </c>
-      <c r="D23" s="3"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="3" t="s">
+      <c r="D23" s="1"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
     </row>
     <row r="24" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C24" s="3">
+      <c r="C24" s="1">
         <v>15</v>
       </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="3" t="s">
+      <c r="D24" s="1"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
     </row>
     <row r="25" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C25" s="3">
+      <c r="C25" s="1">
         <v>16</v>
       </c>
-      <c r="D25" s="3"/>
-      <c r="E25" s="11" t="s">
+      <c r="D25" s="1"/>
+      <c r="E25" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="F25" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
     </row>
     <row r="26" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C26" s="3">
+      <c r="C26" s="1">
         <v>17</v>
       </c>
-      <c r="D26" s="3"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="3" t="s">
+      <c r="D26" s="1"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
     </row>
     <row r="27" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C27" s="3">
+      <c r="C27" s="1">
         <v>18</v>
       </c>
-      <c r="D27" s="3"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="3" t="s">
+      <c r="D27" s="1"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
     </row>
     <row r="28" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C28" s="3">
+      <c r="C28" s="1">
         <v>19</v>
       </c>
-      <c r="D28" s="3"/>
-      <c r="E28" s="11" t="s">
+      <c r="D28" s="1"/>
+      <c r="E28" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="F28" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
     </row>
     <row r="29" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C29" s="3">
+      <c r="C29" s="1">
         <v>20</v>
       </c>
-      <c r="D29" s="3"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="3" t="s">
+      <c r="D29" s="1"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
     </row>
     <row r="30" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C30" s="3">
+      <c r="C30" s="1">
         <v>21</v>
       </c>
-      <c r="D30" s="3"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="3" t="s">
+      <c r="D30" s="1"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
     </row>
     <row r="31" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C31" s="3">
+      <c r="C31" s="1">
         <v>22</v>
       </c>
-      <c r="D31" s="3"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="3" t="s">
+      <c r="D31" s="1"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
     </row>
     <row r="32" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C32" s="3">
+      <c r="C32" s="1">
         <v>23</v>
       </c>
-      <c r="D32" s="3"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="3" t="s">
+      <c r="D32" s="1"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
     </row>
     <row r="33" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C33" s="3">
+      <c r="C33" s="1">
         <v>24</v>
       </c>
-      <c r="D33" s="3"/>
-      <c r="E33" s="11" t="s">
+      <c r="D33" s="1"/>
+      <c r="E33" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="F33" s="12" t="s">
+      <c r="F33" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
     </row>
     <row r="34" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C34" s="3">
+      <c r="C34" s="1">
         <v>25</v>
       </c>
-      <c r="D34" s="3"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="12" t="s">
+      <c r="D34" s="1"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
     </row>
     <row r="35" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C35" s="3">
+      <c r="C35" s="1">
         <v>26</v>
       </c>
-      <c r="D35" s="3"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="12" t="s">
+      <c r="D35" s="1"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
     </row>
     <row r="36" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C36" s="3">
+      <c r="C36" s="1">
         <v>27</v>
       </c>
-      <c r="D36" s="3"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="12" t="s">
+      <c r="D36" s="1"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
     </row>
     <row r="37" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C37" s="3">
+      <c r="C37" s="1">
         <v>28</v>
       </c>
-      <c r="D37" s="3"/>
-      <c r="E37" s="11" t="s">
+      <c r="D37" s="1"/>
+      <c r="E37" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="F37" s="12" t="s">
+      <c r="F37" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G37" s="3"/>
-      <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
     </row>
     <row r="38" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C38" s="3">
+      <c r="C38" s="1">
         <v>29</v>
       </c>
-      <c r="D38" s="3"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="12" t="s">
+      <c r="D38" s="1"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
     </row>
     <row r="39" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C39" s="3">
+      <c r="C39" s="1">
         <v>30</v>
       </c>
-      <c r="D39" s="3"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="12" t="s">
+      <c r="D39" s="1"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
     </row>
     <row r="40" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C40" s="3">
+      <c r="C40" s="1">
         <v>31</v>
       </c>
-      <c r="D40" s="3"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="12" t="s">
+      <c r="D40" s="1"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
-      <c r="I40" s="3"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
     </row>
     <row r="41" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C41" s="3">
+      <c r="C41" s="1">
         <v>32</v>
       </c>
-      <c r="D41" s="3"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="12" t="s">
+      <c r="D41" s="1"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G41" s="3"/>
-      <c r="H41" s="3"/>
-      <c r="I41" s="3"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
     </row>
     <row r="42" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C42" s="3">
+      <c r="C42" s="1">
         <v>33</v>
       </c>
-      <c r="D42" s="3"/>
-      <c r="E42" s="8" t="s">
+      <c r="D42" s="1"/>
+      <c r="E42" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F42" s="3" t="s">
+      <c r="F42" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
     </row>
     <row r="43" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C43" s="3">
+      <c r="C43" s="1">
         <v>34</v>
       </c>
-      <c r="D43" s="3"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="3" t="s">
+      <c r="D43" s="1"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G43" s="3"/>
-      <c r="H43" s="3"/>
-      <c r="I43" s="3"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
     </row>
     <row r="44" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C44" s="3">
+      <c r="C44" s="1">
         <v>35</v>
       </c>
-      <c r="D44" s="3"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="3" t="s">
+      <c r="D44" s="1"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G44" s="3"/>
-      <c r="H44" s="3"/>
-      <c r="I44" s="3"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
     </row>
     <row r="45" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C45" s="3">
+      <c r="C45" s="1">
         <v>36</v>
       </c>
-      <c r="D45" s="3"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="3" t="s">
+      <c r="D45" s="1"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="G45" s="3"/>
-      <c r="H45" s="3"/>
-      <c r="I45" s="3"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
     </row>
     <row r="46" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C46" s="3">
+      <c r="C46" s="1">
         <v>37</v>
       </c>
-      <c r="D46" s="3"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="3" t="s">
+      <c r="D46" s="1"/>
+      <c r="E46" s="9"/>
+      <c r="F46" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G46" s="3"/>
-      <c r="H46" s="3"/>
-      <c r="I46" s="3"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
     </row>
     <row r="47" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C47" s="3">
+      <c r="C47" s="1">
         <v>38</v>
       </c>
-      <c r="D47" s="3"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="10" t="s">
+      <c r="D47" s="1"/>
+      <c r="E47" s="10"/>
+      <c r="F47" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="G47" s="3"/>
-      <c r="H47" s="3"/>
-      <c r="I47" s="3"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
     </row>
     <row r="48" spans="3:9" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="C48" s="3">
+      <c r="C48" s="1">
         <v>39</v>
       </c>
-      <c r="D48" s="3"/>
-      <c r="E48" s="8" t="s">
+      <c r="D48" s="1"/>
+      <c r="E48" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="F48" s="5" t="s">
+      <c r="F48" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G48" s="3"/>
-      <c r="H48" s="3"/>
-      <c r="I48" s="3"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
     </row>
     <row r="49" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C49" s="3">
+      <c r="C49" s="1">
         <v>40</v>
       </c>
-      <c r="D49" s="3"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="3" t="s">
+      <c r="D49" s="1"/>
+      <c r="E49" s="9"/>
+      <c r="F49" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G49" s="3"/>
-      <c r="H49" s="3"/>
-      <c r="I49" s="3"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
     </row>
     <row r="50" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C50" s="3">
+      <c r="C50" s="1">
         <v>41</v>
       </c>
-      <c r="D50" s="3"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="3" t="s">
+      <c r="D50" s="1"/>
+      <c r="E50" s="9"/>
+      <c r="F50" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G50" s="3"/>
-      <c r="H50" s="3"/>
-      <c r="I50" s="3"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
     </row>
     <row r="51" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C51" s="3">
+      <c r="C51" s="1">
         <v>42</v>
       </c>
-      <c r="D51" s="3"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="3" t="s">
+      <c r="D51" s="1"/>
+      <c r="E51" s="10"/>
+      <c r="F51" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G51" s="3"/>
-      <c r="H51" s="3"/>
-      <c r="I51" s="3"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
     </row>
     <row r="52" spans="3:9" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C52" s="3">
+      <c r="C52" s="1">
         <v>43</v>
       </c>
-      <c r="D52" s="3"/>
-      <c r="E52" s="8" t="s">
+      <c r="D52" s="1"/>
+      <c r="E52" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+    </row>
+    <row r="53" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C53" s="1">
+        <v>44</v>
+      </c>
+      <c r="D53" s="1"/>
+      <c r="E53" s="5"/>
+      <c r="F53" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
+    </row>
+    <row r="54" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C54" s="1">
+        <v>45</v>
+      </c>
+      <c r="D54" s="1"/>
+      <c r="E54" s="5"/>
+      <c r="F54" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
+    </row>
+    <row r="55" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C55" s="1">
+        <v>46</v>
+      </c>
+      <c r="D55" s="1"/>
+      <c r="E55" s="5"/>
+      <c r="F55" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+    </row>
+    <row r="56" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C56" s="1">
+        <v>47</v>
+      </c>
+      <c r="D56" s="1"/>
+      <c r="E56" s="5"/>
+      <c r="F56" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F52" s="3" t="s">
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+    </row>
+    <row r="57" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C57" s="1">
+        <v>48</v>
+      </c>
+      <c r="D57" s="1"/>
+      <c r="E57" s="5"/>
+      <c r="F57" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+    </row>
+    <row r="58" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C58" s="1">
+        <v>49</v>
+      </c>
+      <c r="D58" s="1"/>
+      <c r="E58" s="5"/>
+      <c r="F58" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+    </row>
+    <row r="59" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C59" s="1">
+        <v>50</v>
+      </c>
+      <c r="D59" s="1"/>
+      <c r="E59" s="6"/>
+      <c r="F59" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
+      <c r="I59" s="1"/>
+    </row>
+    <row r="60" spans="3:9" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="C60" s="1">
+        <v>51</v>
+      </c>
+      <c r="D60" s="1"/>
+      <c r="E60" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="1"/>
+    </row>
+    <row r="61" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C61" s="1">
+        <v>52</v>
+      </c>
+      <c r="D61" s="1"/>
+      <c r="E61" s="9"/>
+      <c r="F61" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1"/>
+    </row>
+    <row r="62" spans="3:9" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="C62" s="1">
+        <v>53</v>
+      </c>
+      <c r="D62" s="1"/>
+      <c r="E62" s="10"/>
+      <c r="F62" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+    </row>
+    <row r="63" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C63" s="1">
+        <v>54</v>
+      </c>
+      <c r="D63" s="1"/>
+      <c r="E63" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
+    </row>
+    <row r="64" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C64" s="1">
+        <v>55</v>
+      </c>
+      <c r="D64" s="1"/>
+      <c r="E64" s="9"/>
+      <c r="F64" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
+    </row>
+    <row r="65" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C65" s="1">
+        <v>56</v>
+      </c>
+      <c r="D65" s="1"/>
+      <c r="E65" s="10"/>
+      <c r="F65" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
+    </row>
+    <row r="66" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C66" s="1">
+        <v>57</v>
+      </c>
+      <c r="D66" s="1"/>
+      <c r="E66" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+    </row>
+    <row r="67" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C67" s="1">
         <v>58</v>
       </c>
-      <c r="G52" s="3"/>
-      <c r="H52" s="3"/>
-      <c r="I52" s="3"/>
-    </row>
-    <row r="53" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C53" s="3">
-        <v>44</v>
-      </c>
-      <c r="D53" s="3"/>
-      <c r="E53" s="9"/>
-      <c r="F53" s="3" t="s">
+      <c r="D67" s="1"/>
+      <c r="E67" s="9"/>
+      <c r="F67" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="1"/>
+    </row>
+    <row r="68" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C68" s="1">
         <v>59</v>
       </c>
-      <c r="G53" s="3"/>
-      <c r="H53" s="3"/>
-      <c r="I53" s="3"/>
-    </row>
-    <row r="54" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C54" s="3">
-        <v>45</v>
-      </c>
-      <c r="D54" s="3"/>
-      <c r="E54" s="9"/>
-      <c r="F54" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="G54" s="3"/>
-      <c r="H54" s="3"/>
-      <c r="I54" s="3"/>
-    </row>
-    <row r="55" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C55" s="3">
-        <v>46</v>
-      </c>
-      <c r="D55" s="3"/>
-      <c r="E55" s="9"/>
-      <c r="F55" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="G55" s="3"/>
-      <c r="H55" s="3"/>
-      <c r="I55" s="3"/>
-    </row>
-    <row r="56" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C56" s="3">
-        <v>47</v>
-      </c>
-      <c r="D56" s="3"/>
-      <c r="E56" s="9"/>
-      <c r="F56" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="G56" s="3"/>
-      <c r="H56" s="3"/>
-      <c r="I56" s="3"/>
-    </row>
-    <row r="57" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C57" s="3">
-        <v>48</v>
-      </c>
-      <c r="D57" s="3"/>
-      <c r="E57" s="9"/>
-      <c r="F57" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="G57" s="3"/>
-      <c r="H57" s="3"/>
-      <c r="I57" s="3"/>
-    </row>
-    <row r="58" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C58" s="3">
-        <v>49</v>
-      </c>
-      <c r="D58" s="3"/>
-      <c r="E58" s="9"/>
-      <c r="F58" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="G58" s="3"/>
-      <c r="H58" s="3"/>
-      <c r="I58" s="3"/>
-    </row>
-    <row r="59" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C59" s="3">
-        <v>50</v>
-      </c>
-      <c r="D59" s="3"/>
-      <c r="E59" s="13"/>
-      <c r="F59" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G59" s="3"/>
-      <c r="H59" s="3"/>
-      <c r="I59" s="3"/>
-    </row>
-    <row r="60" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C60" s="3">
-        <v>51</v>
-      </c>
-      <c r="D60" s="3"/>
-      <c r="E60" s="3"/>
-      <c r="F60" s="3"/>
-      <c r="G60" s="3"/>
-      <c r="H60" s="3"/>
-      <c r="I60" s="3"/>
-    </row>
-    <row r="61" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C61" s="3">
-        <v>52</v>
-      </c>
-      <c r="D61" s="3"/>
-      <c r="E61" s="3"/>
-      <c r="F61" s="3"/>
-      <c r="G61" s="3"/>
-      <c r="H61" s="3"/>
-      <c r="I61" s="3"/>
-    </row>
-    <row r="62" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C62" s="3">
-        <v>53</v>
-      </c>
-      <c r="D62" s="3"/>
-      <c r="E62" s="3"/>
-      <c r="F62" s="3"/>
-      <c r="G62" s="3"/>
-      <c r="H62" s="3"/>
-      <c r="I62" s="3"/>
-    </row>
-    <row r="63" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C63" s="3">
-        <v>54</v>
-      </c>
-      <c r="D63" s="3"/>
-      <c r="E63" s="3"/>
-      <c r="F63" s="3"/>
-      <c r="G63" s="3"/>
-      <c r="H63" s="3"/>
-      <c r="I63" s="3"/>
+      <c r="D68" s="1"/>
+      <c r="E68" s="10"/>
+      <c r="F68" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+    </row>
+    <row r="69" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C69" s="1"/>
+      <c r="D69" s="1"/>
+      <c r="E69" s="1"/>
+      <c r="F69" s="1"/>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
+    </row>
+    <row r="70" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+    </row>
+    <row r="71" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C71" s="1"/>
+      <c r="D71" s="1"/>
+      <c r="E71" s="1"/>
+      <c r="F71" s="1"/>
+      <c r="G71" s="1"/>
+      <c r="H71" s="1"/>
+      <c r="I71" s="1"/>
+    </row>
+    <row r="72" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C72" s="1"/>
+      <c r="D72" s="1"/>
+      <c r="E72" s="1"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="1"/>
+    </row>
+    <row r="73" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C73" s="1"/>
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1"/>
+    </row>
+    <row r="74" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+    </row>
+    <row r="75" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C75" s="1"/>
+      <c r="D75" s="1"/>
+      <c r="E75" s="1"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
+    </row>
+    <row r="76" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C76" s="1"/>
+      <c r="D76" s="1"/>
+      <c r="E76" s="1"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
+    </row>
+    <row r="77" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C77" s="1"/>
+      <c r="D77" s="1"/>
+      <c r="E77" s="1"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+    </row>
+    <row r="78" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+    </row>
+    <row r="79" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C79" s="1"/>
+      <c r="D79" s="1"/>
+      <c r="E79" s="1"/>
+      <c r="F79" s="1"/>
+      <c r="G79" s="1"/>
+      <c r="H79" s="1"/>
+      <c r="I79" s="1"/>
+    </row>
+    <row r="80" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C80" s="1"/>
+      <c r="D80" s="1"/>
+      <c r="E80" s="1"/>
+      <c r="F80" s="1"/>
+      <c r="G80" s="1"/>
+      <c r="H80" s="1"/>
+      <c r="I80" s="1"/>
+    </row>
+    <row r="81" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C81" s="1"/>
+      <c r="D81" s="1"/>
+      <c r="E81" s="1"/>
+      <c r="F81" s="1"/>
+      <c r="G81" s="1"/>
+      <c r="H81" s="1"/>
+      <c r="I81" s="1"/>
+    </row>
+    <row r="82" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C82" s="1"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="1"/>
+      <c r="F82" s="1"/>
+      <c r="G82" s="1"/>
+      <c r="H82" s="1"/>
+      <c r="I82" s="1"/>
+    </row>
+    <row r="83" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C83" s="1"/>
+      <c r="D83" s="1"/>
+      <c r="E83" s="1"/>
+      <c r="F83" s="1"/>
+      <c r="G83" s="1"/>
+      <c r="H83" s="1"/>
+      <c r="I83" s="1"/>
+    </row>
+    <row r="84" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C84" s="1"/>
+      <c r="D84" s="1"/>
+      <c r="E84" s="1"/>
+      <c r="F84" s="1"/>
+      <c r="G84" s="1"/>
+      <c r="H84" s="1"/>
+      <c r="I84" s="1"/>
+    </row>
+    <row r="85" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C85" s="1"/>
+      <c r="D85" s="1"/>
+      <c r="E85" s="1"/>
+      <c r="F85" s="1"/>
+      <c r="G85" s="1"/>
+      <c r="H85" s="1"/>
+      <c r="I85" s="1"/>
+    </row>
+    <row r="86" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C86" s="1"/>
+      <c r="D86" s="1"/>
+      <c r="E86" s="1"/>
+      <c r="F86" s="1"/>
+      <c r="G86" s="1"/>
+      <c r="H86" s="1"/>
+      <c r="I86" s="1"/>
+    </row>
+    <row r="87" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C87" s="1"/>
+      <c r="D87" s="1"/>
+      <c r="E87" s="1"/>
+      <c r="F87" s="1"/>
+      <c r="G87" s="1"/>
+      <c r="H87" s="1"/>
+      <c r="I87" s="1"/>
+    </row>
+    <row r="88" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C88" s="1"/>
+      <c r="D88" s="1"/>
+      <c r="E88" s="1"/>
+      <c r="F88" s="1"/>
+      <c r="G88" s="1"/>
+      <c r="H88" s="1"/>
+      <c r="I88" s="1"/>
+    </row>
+    <row r="89" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C89" s="1"/>
+      <c r="D89" s="1"/>
+      <c r="E89" s="1"/>
+      <c r="F89" s="1"/>
+      <c r="G89" s="1"/>
+      <c r="H89" s="1"/>
+      <c r="I89" s="1"/>
+    </row>
+    <row r="90" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C90" s="1"/>
+      <c r="D90" s="1"/>
+      <c r="E90" s="1"/>
+      <c r="F90" s="1"/>
+      <c r="G90" s="1"/>
+      <c r="H90" s="1"/>
+      <c r="I90" s="1"/>
+    </row>
+    <row r="91" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C91" s="1"/>
+      <c r="D91" s="1"/>
+      <c r="E91" s="1"/>
+      <c r="F91" s="1"/>
+      <c r="G91" s="1"/>
+      <c r="H91" s="1"/>
+      <c r="I91" s="1"/>
+    </row>
+    <row r="92" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C92" s="1"/>
+      <c r="D92" s="1"/>
+      <c r="E92" s="1"/>
+      <c r="F92" s="1"/>
+      <c r="G92" s="1"/>
+      <c r="H92" s="1"/>
+      <c r="I92" s="1"/>
+    </row>
+    <row r="93" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C93" s="1"/>
+      <c r="D93" s="1"/>
+      <c r="E93" s="1"/>
+      <c r="F93" s="1"/>
+      <c r="G93" s="1"/>
+      <c r="H93" s="1"/>
+      <c r="I93" s="1"/>
+    </row>
+    <row r="94" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C94" s="1"/>
+      <c r="D94" s="1"/>
+      <c r="E94" s="1"/>
+      <c r="F94" s="1"/>
+      <c r="G94" s="1"/>
+      <c r="H94" s="1"/>
+      <c r="I94" s="1"/>
+    </row>
+    <row r="95" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C95" s="1"/>
+      <c r="D95" s="1"/>
+      <c r="E95" s="1"/>
+      <c r="F95" s="1"/>
+      <c r="G95" s="1"/>
+      <c r="H95" s="1"/>
+      <c r="I95" s="1"/>
+    </row>
+    <row r="96" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C96" s="1"/>
+      <c r="D96" s="1"/>
+      <c r="E96" s="1"/>
+      <c r="F96" s="1"/>
+      <c r="G96" s="1"/>
+      <c r="H96" s="1"/>
+      <c r="I96" s="1"/>
+    </row>
+    <row r="97" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C97" s="1"/>
+      <c r="D97" s="1"/>
+      <c r="E97" s="1"/>
+      <c r="F97" s="1"/>
+      <c r="G97" s="1"/>
+      <c r="H97" s="1"/>
+      <c r="I97" s="1"/>
+    </row>
+    <row r="98" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C98" s="1"/>
+      <c r="D98" s="1"/>
+      <c r="E98" s="1"/>
+      <c r="F98" s="1"/>
+      <c r="G98" s="1"/>
+      <c r="H98" s="1"/>
+      <c r="I98" s="1"/>
+    </row>
+    <row r="99" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C99" s="1"/>
+      <c r="D99" s="1"/>
+      <c r="E99" s="1"/>
+      <c r="F99" s="1"/>
+      <c r="G99" s="1"/>
+      <c r="H99" s="1"/>
+      <c r="I99" s="1"/>
+    </row>
+    <row r="100" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C100" s="1"/>
+      <c r="D100" s="1"/>
+      <c r="E100" s="1"/>
+      <c r="F100" s="1"/>
+      <c r="G100" s="1"/>
+      <c r="H100" s="1"/>
+      <c r="I100" s="1"/>
+    </row>
+    <row r="101" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C101" s="1"/>
+      <c r="D101" s="1"/>
+      <c r="E101" s="1"/>
+      <c r="F101" s="1"/>
+      <c r="G101" s="1"/>
+      <c r="H101" s="1"/>
+      <c r="I101" s="1"/>
+    </row>
+    <row r="102" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C102" s="1"/>
+      <c r="D102" s="1"/>
+      <c r="E102" s="1"/>
+      <c r="F102" s="1"/>
+      <c r="G102" s="1"/>
+      <c r="H102" s="1"/>
+      <c r="I102" s="1"/>
+    </row>
+    <row r="103" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C103" s="1"/>
+      <c r="D103" s="1"/>
+      <c r="E103" s="1"/>
+      <c r="F103" s="1"/>
+      <c r="G103" s="1"/>
+      <c r="H103" s="1"/>
+      <c r="I103" s="1"/>
+    </row>
+    <row r="104" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C104" s="1"/>
+      <c r="D104" s="1"/>
+      <c r="E104" s="1"/>
+      <c r="F104" s="1"/>
+      <c r="G104" s="1"/>
+      <c r="H104" s="1"/>
+      <c r="I104" s="1"/>
+    </row>
+    <row r="105" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C105" s="1"/>
+      <c r="D105" s="1"/>
+      <c r="E105" s="1"/>
+      <c r="F105" s="1"/>
+      <c r="G105" s="1"/>
+      <c r="H105" s="1"/>
+      <c r="I105" s="1"/>
+    </row>
+    <row r="106" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C106" s="1"/>
+      <c r="D106" s="1"/>
+      <c r="E106" s="1"/>
+      <c r="F106" s="1"/>
+      <c r="G106" s="1"/>
+      <c r="H106" s="1"/>
+      <c r="I106" s="1"/>
+    </row>
+    <row r="107" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C107" s="1"/>
+      <c r="D107" s="1"/>
+      <c r="E107" s="1"/>
+      <c r="F107" s="1"/>
+      <c r="G107" s="1"/>
+      <c r="H107" s="1"/>
+      <c r="I107" s="1"/>
+    </row>
+    <row r="108" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C108" s="1"/>
+      <c r="D108" s="1"/>
+      <c r="E108" s="1"/>
+      <c r="F108" s="1"/>
+      <c r="G108" s="1"/>
+      <c r="H108" s="1"/>
+      <c r="I108" s="1"/>
+    </row>
+    <row r="109" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C109" s="1"/>
+      <c r="D109" s="1"/>
+      <c r="E109" s="1"/>
+      <c r="F109" s="1"/>
+      <c r="G109" s="1"/>
+      <c r="H109" s="1"/>
+      <c r="I109" s="1"/>
+    </row>
+    <row r="110" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C110" s="1"/>
+      <c r="D110" s="1"/>
+      <c r="E110" s="1"/>
+      <c r="F110" s="1"/>
+      <c r="G110" s="1"/>
+      <c r="H110" s="1"/>
+      <c r="I110" s="1"/>
+    </row>
+    <row r="111" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C111" s="1"/>
+      <c r="D111" s="1"/>
+      <c r="E111" s="1"/>
+      <c r="F111" s="1"/>
+      <c r="G111" s="1"/>
+      <c r="H111" s="1"/>
+      <c r="I111" s="1"/>
+    </row>
+    <row r="112" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C112" s="1"/>
+      <c r="D112" s="1"/>
+      <c r="E112" s="1"/>
+      <c r="F112" s="1"/>
+      <c r="G112" s="1"/>
+      <c r="H112" s="1"/>
+      <c r="I112" s="1"/>
+    </row>
+    <row r="113" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C113" s="1"/>
+      <c r="D113" s="1"/>
+      <c r="E113" s="1"/>
+      <c r="F113" s="1"/>
+      <c r="G113" s="1"/>
+      <c r="H113" s="1"/>
+      <c r="I113" s="1"/>
+    </row>
+    <row r="114" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C114" s="1"/>
+      <c r="D114" s="1"/>
+      <c r="E114" s="1"/>
+      <c r="F114" s="1"/>
+      <c r="G114" s="1"/>
+      <c r="H114" s="1"/>
+      <c r="I114" s="1"/>
+    </row>
+    <row r="115" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C115" s="1"/>
+      <c r="D115" s="1"/>
+      <c r="E115" s="1"/>
+      <c r="F115" s="1"/>
+      <c r="G115" s="1"/>
+      <c r="H115" s="1"/>
+      <c r="I115" s="1"/>
+    </row>
+    <row r="116" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C116" s="1"/>
+      <c r="D116" s="1"/>
+      <c r="E116" s="1"/>
+      <c r="F116" s="1"/>
+      <c r="G116" s="1"/>
+      <c r="H116" s="1"/>
+      <c r="I116" s="1"/>
+    </row>
+    <row r="117" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C117" s="1"/>
+      <c r="D117" s="1"/>
+      <c r="E117" s="1"/>
+      <c r="F117" s="1"/>
+      <c r="G117" s="1"/>
+      <c r="H117" s="1"/>
+      <c r="I117" s="1"/>
+    </row>
+    <row r="118" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C118" s="1"/>
+      <c r="D118" s="1"/>
+      <c r="E118" s="1"/>
+      <c r="F118" s="1"/>
+      <c r="G118" s="1"/>
+      <c r="H118" s="1"/>
+      <c r="I118" s="1"/>
+    </row>
+    <row r="119" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C119" s="1"/>
+      <c r="D119" s="1"/>
+      <c r="E119" s="1"/>
+      <c r="F119" s="1"/>
+      <c r="G119" s="1"/>
+      <c r="H119" s="1"/>
+      <c r="I119" s="1"/>
+    </row>
+    <row r="120" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C120" s="1"/>
+      <c r="D120" s="1"/>
+      <c r="E120" s="1"/>
+      <c r="F120" s="1"/>
+      <c r="G120" s="1"/>
+      <c r="H120" s="1"/>
+      <c r="I120" s="1"/>
+    </row>
+    <row r="121" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C121" s="1"/>
+      <c r="D121" s="1"/>
+      <c r="E121" s="1"/>
+      <c r="F121" s="1"/>
+      <c r="G121" s="1"/>
+      <c r="H121" s="1"/>
+      <c r="I121" s="1"/>
+    </row>
+    <row r="122" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C122" s="1"/>
+      <c r="D122" s="1"/>
+      <c r="E122" s="1"/>
+      <c r="F122" s="1"/>
+      <c r="G122" s="1"/>
+      <c r="H122" s="1"/>
+      <c r="I122" s="1"/>
+    </row>
+    <row r="123" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C123" s="1"/>
+      <c r="D123" s="1"/>
+      <c r="E123" s="1"/>
+      <c r="F123" s="1"/>
+      <c r="G123" s="1"/>
+      <c r="H123" s="1"/>
+      <c r="I123" s="1"/>
+    </row>
+    <row r="124" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C124" s="1"/>
+      <c r="D124" s="1"/>
+      <c r="E124" s="1"/>
+      <c r="F124" s="1"/>
+      <c r="G124" s="1"/>
+      <c r="H124" s="1"/>
+      <c r="I124" s="1"/>
+    </row>
+    <row r="125" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C125" s="1"/>
+      <c r="D125" s="1"/>
+      <c r="E125" s="1"/>
+      <c r="F125" s="1"/>
+      <c r="G125" s="1"/>
+      <c r="H125" s="1"/>
+      <c r="I125" s="1"/>
+    </row>
+    <row r="126" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C126" s="1"/>
+      <c r="D126" s="1"/>
+      <c r="E126" s="1"/>
+      <c r="F126" s="1"/>
+      <c r="G126" s="1"/>
+      <c r="H126" s="1"/>
+      <c r="I126" s="1"/>
+    </row>
+    <row r="127" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C127" s="1"/>
+      <c r="D127" s="1"/>
+      <c r="E127" s="1"/>
+      <c r="F127" s="1"/>
+      <c r="G127" s="1"/>
+      <c r="H127" s="1"/>
+      <c r="I127" s="1"/>
+    </row>
+    <row r="128" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C128" s="1"/>
+      <c r="D128" s="1"/>
+      <c r="E128" s="1"/>
+      <c r="F128" s="1"/>
+      <c r="G128" s="1"/>
+      <c r="H128" s="1"/>
+      <c r="I128" s="1"/>
+    </row>
+    <row r="129" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C129" s="1"/>
+      <c r="D129" s="1"/>
+      <c r="E129" s="1"/>
+      <c r="F129" s="1"/>
+      <c r="G129" s="1"/>
+      <c r="H129" s="1"/>
+      <c r="I129" s="1"/>
+    </row>
+    <row r="130" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C130" s="1"/>
+      <c r="D130" s="1"/>
+      <c r="E130" s="1"/>
+      <c r="F130" s="1"/>
+      <c r="G130" s="1"/>
+      <c r="H130" s="1"/>
+      <c r="I130" s="1"/>
+    </row>
+    <row r="131" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C131" s="1"/>
+      <c r="D131" s="1"/>
+      <c r="E131" s="1"/>
+      <c r="F131" s="1"/>
+      <c r="G131" s="1"/>
+      <c r="H131" s="1"/>
+      <c r="I131" s="1"/>
+    </row>
+    <row r="132" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C132" s="1"/>
+      <c r="D132" s="1"/>
+      <c r="E132" s="1"/>
+      <c r="F132" s="1"/>
+      <c r="G132" s="1"/>
+      <c r="H132" s="1"/>
+      <c r="I132" s="1"/>
+    </row>
+    <row r="133" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C133" s="1"/>
+      <c r="D133" s="1"/>
+      <c r="E133" s="1"/>
+      <c r="F133" s="1"/>
+      <c r="G133" s="1"/>
+      <c r="H133" s="1"/>
+      <c r="I133" s="1"/>
+    </row>
+    <row r="134" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C134" s="1"/>
+      <c r="D134" s="1"/>
+      <c r="E134" s="1"/>
+      <c r="F134" s="1"/>
+      <c r="G134" s="1"/>
+      <c r="H134" s="1"/>
+      <c r="I134" s="1"/>
+    </row>
+    <row r="135" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C135" s="1"/>
+      <c r="D135" s="1"/>
+      <c r="E135" s="1"/>
+      <c r="F135" s="1"/>
+      <c r="G135" s="1"/>
+      <c r="H135" s="1"/>
+      <c r="I135" s="1"/>
+    </row>
+    <row r="136" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C136" s="1"/>
+      <c r="D136" s="1"/>
+      <c r="E136" s="1"/>
+      <c r="F136" s="1"/>
+      <c r="G136" s="1"/>
+      <c r="H136" s="1"/>
+      <c r="I136" s="1"/>
+    </row>
+    <row r="137" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C137" s="1"/>
+      <c r="D137" s="1"/>
+      <c r="E137" s="1"/>
+      <c r="F137" s="1"/>
+      <c r="G137" s="1"/>
+      <c r="H137" s="1"/>
+      <c r="I137" s="1"/>
+    </row>
+    <row r="138" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C138" s="1"/>
+      <c r="D138" s="1"/>
+      <c r="E138" s="1"/>
+      <c r="F138" s="1"/>
+      <c r="G138" s="1"/>
+      <c r="H138" s="1"/>
+      <c r="I138" s="1"/>
+    </row>
+    <row r="139" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C139" s="1"/>
+      <c r="D139" s="1"/>
+      <c r="E139" s="1"/>
+      <c r="F139" s="1"/>
+      <c r="G139" s="1"/>
+      <c r="H139" s="1"/>
+      <c r="I139" s="1"/>
+    </row>
+    <row r="140" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C140" s="1"/>
+      <c r="D140" s="1"/>
+      <c r="E140" s="1"/>
+      <c r="F140" s="1"/>
+      <c r="G140" s="1"/>
+      <c r="H140" s="1"/>
+      <c r="I140" s="1"/>
+    </row>
+    <row r="141" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C141" s="1"/>
+      <c r="D141" s="1"/>
+      <c r="E141" s="1"/>
+      <c r="F141" s="1"/>
+      <c r="G141" s="1"/>
+      <c r="H141" s="1"/>
+      <c r="I141" s="1"/>
+    </row>
+    <row r="142" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C142" s="1"/>
+      <c r="D142" s="1"/>
+      <c r="E142" s="1"/>
+      <c r="F142" s="1"/>
+      <c r="G142" s="1"/>
+      <c r="H142" s="1"/>
+      <c r="I142" s="1"/>
+    </row>
+    <row r="143" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C143" s="1"/>
+      <c r="D143" s="1"/>
+      <c r="E143" s="1"/>
+      <c r="F143" s="1"/>
+      <c r="G143" s="1"/>
+      <c r="H143" s="1"/>
+      <c r="I143" s="1"/>
+    </row>
+    <row r="144" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C144" s="1"/>
+      <c r="D144" s="1"/>
+      <c r="E144" s="1"/>
+      <c r="F144" s="1"/>
+      <c r="G144" s="1"/>
+      <c r="H144" s="1"/>
+      <c r="I144" s="1"/>
+    </row>
+    <row r="145" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C145" s="1"/>
+      <c r="D145" s="1"/>
+      <c r="E145" s="1"/>
+      <c r="F145" s="1"/>
+      <c r="G145" s="1"/>
+      <c r="H145" s="1"/>
+      <c r="I145" s="1"/>
+    </row>
+    <row r="146" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C146" s="1"/>
+      <c r="D146" s="1"/>
+      <c r="E146" s="1"/>
+      <c r="F146" s="1"/>
+      <c r="G146" s="1"/>
+      <c r="H146" s="1"/>
+      <c r="I146" s="1"/>
+    </row>
+    <row r="147" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C147" s="1"/>
+      <c r="D147" s="1"/>
+      <c r="E147" s="1"/>
+      <c r="F147" s="1"/>
+      <c r="G147" s="1"/>
+      <c r="H147" s="1"/>
+      <c r="I147" s="1"/>
+    </row>
+    <row r="148" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C148" s="1"/>
+      <c r="D148" s="1"/>
+      <c r="E148" s="1"/>
+      <c r="F148" s="1"/>
+      <c r="G148" s="1"/>
+      <c r="H148" s="1"/>
+      <c r="I148" s="1"/>
+    </row>
+    <row r="149" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C149" s="1"/>
+      <c r="D149" s="1"/>
+      <c r="E149" s="1"/>
+      <c r="F149" s="1"/>
+      <c r="G149" s="1"/>
+      <c r="H149" s="1"/>
+      <c r="I149" s="1"/>
+    </row>
+    <row r="150" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C150" s="1"/>
+      <c r="D150" s="1"/>
+      <c r="E150" s="1"/>
+      <c r="F150" s="1"/>
+      <c r="G150" s="1"/>
+      <c r="H150" s="1"/>
+      <c r="I150" s="1"/>
+    </row>
+    <row r="151" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C151" s="1"/>
+      <c r="D151" s="1"/>
+      <c r="E151" s="1"/>
+      <c r="F151" s="1"/>
+      <c r="G151" s="1"/>
+      <c r="H151" s="1"/>
+      <c r="I151" s="1"/>
+    </row>
+    <row r="152" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C152" s="1"/>
+      <c r="D152" s="1"/>
+      <c r="E152" s="1"/>
+      <c r="F152" s="1"/>
+      <c r="G152" s="1"/>
+      <c r="H152" s="1"/>
+      <c r="I152" s="1"/>
+    </row>
+    <row r="153" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C153" s="1"/>
+      <c r="D153" s="1"/>
+      <c r="E153" s="1"/>
+      <c r="F153" s="1"/>
+      <c r="G153" s="1"/>
+      <c r="H153" s="1"/>
+      <c r="I153" s="1"/>
+    </row>
+    <row r="154" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C154" s="1"/>
+      <c r="D154" s="1"/>
+      <c r="E154" s="1"/>
+      <c r="F154" s="1"/>
+      <c r="G154" s="1"/>
+      <c r="H154" s="1"/>
+      <c r="I154" s="1"/>
+    </row>
+    <row r="155" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C155" s="1"/>
+      <c r="D155" s="1"/>
+      <c r="E155" s="1"/>
+      <c r="F155" s="1"/>
+      <c r="G155" s="1"/>
+      <c r="H155" s="1"/>
+      <c r="I155" s="1"/>
+    </row>
+    <row r="156" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C156" s="1"/>
+      <c r="D156" s="1"/>
+      <c r="E156" s="1"/>
+      <c r="F156" s="1"/>
+      <c r="G156" s="1"/>
+      <c r="H156" s="1"/>
+      <c r="I156" s="1"/>
+    </row>
+    <row r="157" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C157" s="1"/>
+      <c r="D157" s="1"/>
+      <c r="E157" s="1"/>
+      <c r="F157" s="1"/>
+      <c r="G157" s="1"/>
+      <c r="H157" s="1"/>
+      <c r="I157" s="1"/>
+    </row>
+    <row r="158" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C158" s="1"/>
+      <c r="D158" s="1"/>
+      <c r="E158" s="1"/>
+      <c r="F158" s="1"/>
+      <c r="G158" s="1"/>
+      <c r="H158" s="1"/>
+      <c r="I158" s="1"/>
+    </row>
+    <row r="159" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C159" s="1"/>
+      <c r="D159" s="1"/>
+      <c r="E159" s="1"/>
+      <c r="F159" s="1"/>
+      <c r="G159" s="1"/>
+      <c r="H159" s="1"/>
+      <c r="I159" s="1"/>
+    </row>
+    <row r="160" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C160" s="1"/>
+      <c r="D160" s="1"/>
+      <c r="E160" s="1"/>
+      <c r="F160" s="1"/>
+      <c r="G160" s="1"/>
+      <c r="H160" s="1"/>
+      <c r="I160" s="1"/>
+    </row>
+    <row r="161" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C161" s="1"/>
+      <c r="D161" s="1"/>
+      <c r="E161" s="1"/>
+      <c r="F161" s="1"/>
+      <c r="G161" s="1"/>
+      <c r="H161" s="1"/>
+      <c r="I161" s="1"/>
+    </row>
+    <row r="162" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C162" s="1"/>
+      <c r="D162" s="1"/>
+      <c r="E162" s="1"/>
+      <c r="F162" s="1"/>
+      <c r="G162" s="1"/>
+      <c r="H162" s="1"/>
+      <c r="I162" s="1"/>
+    </row>
+    <row r="163" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C163" s="1"/>
+      <c r="D163" s="1"/>
+      <c r="E163" s="1"/>
+      <c r="F163" s="1"/>
+      <c r="G163" s="1"/>
+      <c r="H163" s="1"/>
+      <c r="I163" s="1"/>
+    </row>
+    <row r="164" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C164" s="1"/>
+      <c r="D164" s="1"/>
+      <c r="E164" s="1"/>
+      <c r="F164" s="1"/>
+      <c r="G164" s="1"/>
+      <c r="H164" s="1"/>
+      <c r="I164" s="1"/>
+    </row>
+    <row r="165" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C165" s="1"/>
+      <c r="D165" s="1"/>
+      <c r="E165" s="1"/>
+      <c r="F165" s="1"/>
+      <c r="G165" s="1"/>
+      <c r="H165" s="1"/>
+      <c r="I165" s="1"/>
+    </row>
+    <row r="166" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C166" s="1"/>
+      <c r="D166" s="1"/>
+      <c r="E166" s="1"/>
+      <c r="F166" s="1"/>
+      <c r="G166" s="1"/>
+      <c r="H166" s="1"/>
+      <c r="I166" s="1"/>
+    </row>
+    <row r="167" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C167" s="1"/>
+      <c r="D167" s="1"/>
+      <c r="E167" s="1"/>
+      <c r="F167" s="1"/>
+      <c r="G167" s="1"/>
+      <c r="H167" s="1"/>
+      <c r="I167" s="1"/>
+    </row>
+    <row r="168" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C168" s="1"/>
+      <c r="D168" s="1"/>
+      <c r="E168" s="1"/>
+      <c r="F168" s="1"/>
+      <c r="G168" s="1"/>
+      <c r="H168" s="1"/>
+      <c r="I168" s="1"/>
+    </row>
+    <row r="169" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C169" s="1"/>
+      <c r="D169" s="1"/>
+      <c r="E169" s="1"/>
+      <c r="F169" s="1"/>
+      <c r="G169" s="1"/>
+      <c r="H169" s="1"/>
+      <c r="I169" s="1"/>
+    </row>
+    <row r="170" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C170" s="1"/>
+      <c r="D170" s="1"/>
+      <c r="E170" s="1"/>
+      <c r="F170" s="1"/>
+      <c r="G170" s="1"/>
+      <c r="H170" s="1"/>
+      <c r="I170" s="1"/>
+    </row>
+    <row r="171" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C171" s="1"/>
+      <c r="D171" s="1"/>
+      <c r="E171" s="1"/>
+      <c r="F171" s="1"/>
+      <c r="G171" s="1"/>
+      <c r="H171" s="1"/>
+      <c r="I171" s="1"/>
+    </row>
+    <row r="172" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C172" s="1"/>
+      <c r="D172" s="1"/>
+      <c r="E172" s="1"/>
+      <c r="F172" s="1"/>
+      <c r="G172" s="1"/>
+      <c r="H172" s="1"/>
+      <c r="I172" s="1"/>
+    </row>
+    <row r="173" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C173" s="1"/>
+      <c r="D173" s="1"/>
+      <c r="E173" s="1"/>
+      <c r="F173" s="1"/>
+      <c r="G173" s="1"/>
+      <c r="H173" s="1"/>
+      <c r="I173" s="1"/>
+    </row>
+    <row r="174" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C174" s="1"/>
+      <c r="D174" s="1"/>
+      <c r="E174" s="1"/>
+      <c r="F174" s="1"/>
+      <c r="G174" s="1"/>
+      <c r="H174" s="1"/>
+      <c r="I174" s="1"/>
+    </row>
+    <row r="175" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C175" s="1"/>
+      <c r="D175" s="1"/>
+      <c r="E175" s="1"/>
+      <c r="F175" s="1"/>
+      <c r="G175" s="1"/>
+      <c r="H175" s="1"/>
+      <c r="I175" s="1"/>
+    </row>
+    <row r="176" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C176" s="1"/>
+      <c r="D176" s="1"/>
+      <c r="E176" s="1"/>
+      <c r="F176" s="1"/>
+      <c r="G176" s="1"/>
+      <c r="H176" s="1"/>
+      <c r="I176" s="1"/>
+    </row>
+    <row r="177" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C177" s="1"/>
+      <c r="D177" s="1"/>
+      <c r="E177" s="1"/>
+      <c r="F177" s="1"/>
+      <c r="G177" s="1"/>
+      <c r="H177" s="1"/>
+      <c r="I177" s="1"/>
+    </row>
+    <row r="178" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C178" s="1"/>
+      <c r="D178" s="1"/>
+      <c r="E178" s="1"/>
+      <c r="F178" s="1"/>
+      <c r="G178" s="1"/>
+      <c r="H178" s="1"/>
+      <c r="I178" s="1"/>
+    </row>
+    <row r="179" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C179" s="1"/>
+      <c r="D179" s="1"/>
+      <c r="E179" s="1"/>
+      <c r="F179" s="1"/>
+      <c r="G179" s="1"/>
+      <c r="H179" s="1"/>
+      <c r="I179" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="13">
+    <mergeCell ref="E63:E65"/>
+    <mergeCell ref="E66:E68"/>
+    <mergeCell ref="C8:I8"/>
+    <mergeCell ref="E25:E27"/>
+    <mergeCell ref="E17:E24"/>
+    <mergeCell ref="E10:E16"/>
+    <mergeCell ref="E60:E62"/>
     <mergeCell ref="E52:E59"/>
     <mergeCell ref="E28:E32"/>
     <mergeCell ref="E33:E36"/>
     <mergeCell ref="E37:E41"/>
     <mergeCell ref="E42:E47"/>
     <mergeCell ref="E48:E51"/>
-    <mergeCell ref="C8:I8"/>
-    <mergeCell ref="E25:E27"/>
-    <mergeCell ref="E17:E24"/>
-    <mergeCell ref="E10:E16"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Diary/凯哥高数复习规划.xlsx
+++ b/Diary/凯哥高数复习规划.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD51CA60-870A-45F5-AE0E-1DD41D8ECA3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7067E47E-3730-4437-8526-7528A39CA261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -391,12 +391,18 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="5">
@@ -478,10 +484,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -490,18 +499,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -794,15 +800,15 @@
   </cols>
   <sheetData>
     <row r="8" spans="3:9" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
     </row>
     <row r="9" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C9" s="1" t="s">
@@ -832,10 +838,10 @@
         <v>1</v>
       </c>
       <c r="D10" s="1"/>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="12" t="s">
         <v>7</v>
       </c>
       <c r="G10" s="1"/>
@@ -847,8 +853,8 @@
         <v>2</v>
       </c>
       <c r="D11" s="1"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="1" t="s">
+      <c r="E11" s="8"/>
+      <c r="F11" s="13" t="s">
         <v>8</v>
       </c>
       <c r="G11" s="1"/>
@@ -860,8 +866,8 @@
         <v>3</v>
       </c>
       <c r="D12" s="1"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="1" t="s">
+      <c r="E12" s="8"/>
+      <c r="F12" s="13" t="s">
         <v>9</v>
       </c>
       <c r="G12" s="1"/>
@@ -873,8 +879,8 @@
         <v>4</v>
       </c>
       <c r="D13" s="1"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="1" t="s">
+      <c r="E13" s="8"/>
+      <c r="F13" s="13" t="s">
         <v>10</v>
       </c>
       <c r="G13" s="1"/>
@@ -886,8 +892,8 @@
         <v>5</v>
       </c>
       <c r="D14" s="1"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="1" t="s">
+      <c r="E14" s="8"/>
+      <c r="F14" s="13" t="s">
         <v>11</v>
       </c>
       <c r="G14" s="1"/>
@@ -899,8 +905,8 @@
         <v>6</v>
       </c>
       <c r="D15" s="1"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="1" t="s">
+      <c r="E15" s="8"/>
+      <c r="F15" s="13" t="s">
         <v>12</v>
       </c>
       <c r="G15" s="1"/>
@@ -912,7 +918,7 @@
         <v>7</v>
       </c>
       <c r="D16" s="1"/>
-      <c r="E16" s="7"/>
+      <c r="E16" s="8"/>
       <c r="F16" s="1" t="s">
         <v>13</v>
       </c>
@@ -925,7 +931,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="1"/>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="8" t="s">
         <v>23</v>
       </c>
       <c r="F17" s="1" t="s">
@@ -940,7 +946,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="1"/>
-      <c r="E18" s="8"/>
+      <c r="E18" s="9"/>
       <c r="F18" s="1" t="s">
         <v>15</v>
       </c>
@@ -953,7 +959,7 @@
         <v>10</v>
       </c>
       <c r="D19" s="1"/>
-      <c r="E19" s="8"/>
+      <c r="E19" s="9"/>
       <c r="F19" s="1" t="s">
         <v>16</v>
       </c>
@@ -966,7 +972,7 @@
         <v>11</v>
       </c>
       <c r="D20" s="1"/>
-      <c r="E20" s="8"/>
+      <c r="E20" s="9"/>
       <c r="F20" s="1" t="s">
         <v>17</v>
       </c>
@@ -979,7 +985,7 @@
         <v>12</v>
       </c>
       <c r="D21" s="1"/>
-      <c r="E21" s="8"/>
+      <c r="E21" s="9"/>
       <c r="F21" s="1" t="s">
         <v>18</v>
       </c>
@@ -992,7 +998,7 @@
         <v>13</v>
       </c>
       <c r="D22" s="1"/>
-      <c r="E22" s="8"/>
+      <c r="E22" s="9"/>
       <c r="F22" s="1" t="s">
         <v>19</v>
       </c>
@@ -1005,7 +1011,7 @@
         <v>14</v>
       </c>
       <c r="D23" s="1"/>
-      <c r="E23" s="8"/>
+      <c r="E23" s="9"/>
       <c r="F23" s="1" t="s">
         <v>20</v>
       </c>
@@ -1018,7 +1024,7 @@
         <v>15</v>
       </c>
       <c r="D24" s="1"/>
-      <c r="E24" s="8"/>
+      <c r="E24" s="9"/>
       <c r="F24" s="1" t="s">
         <v>21</v>
       </c>
@@ -1031,7 +1037,7 @@
         <v>16</v>
       </c>
       <c r="D25" s="1"/>
-      <c r="E25" s="7" t="s">
+      <c r="E25" s="8" t="s">
         <v>27</v>
       </c>
       <c r="F25" s="2" t="s">
@@ -1046,7 +1052,7 @@
         <v>17</v>
       </c>
       <c r="D26" s="1"/>
-      <c r="E26" s="8"/>
+      <c r="E26" s="9"/>
       <c r="F26" s="1" t="s">
         <v>25</v>
       </c>
@@ -1059,7 +1065,7 @@
         <v>18</v>
       </c>
       <c r="D27" s="1"/>
-      <c r="E27" s="8"/>
+      <c r="E27" s="9"/>
       <c r="F27" s="1" t="s">
         <v>26</v>
       </c>
@@ -1072,7 +1078,7 @@
         <v>19</v>
       </c>
       <c r="D28" s="1"/>
-      <c r="E28" s="7" t="s">
+      <c r="E28" s="8" t="s">
         <v>34</v>
       </c>
       <c r="F28" s="1" t="s">
@@ -1087,7 +1093,7 @@
         <v>20</v>
       </c>
       <c r="D29" s="1"/>
-      <c r="E29" s="8"/>
+      <c r="E29" s="9"/>
       <c r="F29" s="1" t="s">
         <v>30</v>
       </c>
@@ -1100,7 +1106,7 @@
         <v>21</v>
       </c>
       <c r="D30" s="1"/>
-      <c r="E30" s="8"/>
+      <c r="E30" s="9"/>
       <c r="F30" s="1" t="s">
         <v>31</v>
       </c>
@@ -1113,7 +1119,7 @@
         <v>22</v>
       </c>
       <c r="D31" s="1"/>
-      <c r="E31" s="8"/>
+      <c r="E31" s="9"/>
       <c r="F31" s="1" t="s">
         <v>32</v>
       </c>
@@ -1126,7 +1132,7 @@
         <v>23</v>
       </c>
       <c r="D32" s="1"/>
-      <c r="E32" s="8"/>
+      <c r="E32" s="9"/>
       <c r="F32" s="1" t="s">
         <v>33</v>
       </c>
@@ -1139,7 +1145,7 @@
         <v>24</v>
       </c>
       <c r="D33" s="1"/>
-      <c r="E33" s="7" t="s">
+      <c r="E33" s="8" t="s">
         <v>39</v>
       </c>
       <c r="F33" s="1" t="s">
@@ -1154,7 +1160,7 @@
         <v>25</v>
       </c>
       <c r="D34" s="1"/>
-      <c r="E34" s="8"/>
+      <c r="E34" s="9"/>
       <c r="F34" s="1" t="s">
         <v>37</v>
       </c>
@@ -1167,7 +1173,7 @@
         <v>26</v>
       </c>
       <c r="D35" s="1"/>
-      <c r="E35" s="8"/>
+      <c r="E35" s="9"/>
       <c r="F35" s="1" t="s">
         <v>36</v>
       </c>
@@ -1180,7 +1186,7 @@
         <v>27</v>
       </c>
       <c r="D36" s="1"/>
-      <c r="E36" s="8"/>
+      <c r="E36" s="9"/>
       <c r="F36" s="1" t="s">
         <v>38</v>
       </c>
@@ -1193,7 +1199,7 @@
         <v>28</v>
       </c>
       <c r="D37" s="1"/>
-      <c r="E37" s="7" t="s">
+      <c r="E37" s="8" t="s">
         <v>45</v>
       </c>
       <c r="F37" s="1" t="s">
@@ -1208,7 +1214,7 @@
         <v>29</v>
       </c>
       <c r="D38" s="1"/>
-      <c r="E38" s="8"/>
+      <c r="E38" s="9"/>
       <c r="F38" s="1" t="s">
         <v>41</v>
       </c>
@@ -1221,7 +1227,7 @@
         <v>30</v>
       </c>
       <c r="D39" s="1"/>
-      <c r="E39" s="8"/>
+      <c r="E39" s="9"/>
       <c r="F39" s="1" t="s">
         <v>42</v>
       </c>
@@ -1234,7 +1240,7 @@
         <v>31</v>
       </c>
       <c r="D40" s="1"/>
-      <c r="E40" s="8"/>
+      <c r="E40" s="9"/>
       <c r="F40" s="1" t="s">
         <v>43</v>
       </c>
@@ -1247,7 +1253,7 @@
         <v>32</v>
       </c>
       <c r="D41" s="1"/>
-      <c r="E41" s="8"/>
+      <c r="E41" s="9"/>
       <c r="F41" s="1" t="s">
         <v>44</v>
       </c>
@@ -1275,7 +1281,7 @@
         <v>34</v>
       </c>
       <c r="D43" s="1"/>
-      <c r="E43" s="9"/>
+      <c r="E43" s="5"/>
       <c r="F43" s="1" t="s">
         <v>47</v>
       </c>
@@ -1288,7 +1294,7 @@
         <v>35</v>
       </c>
       <c r="D44" s="1"/>
-      <c r="E44" s="9"/>
+      <c r="E44" s="5"/>
       <c r="F44" s="1" t="s">
         <v>48</v>
       </c>
@@ -1301,7 +1307,7 @@
         <v>36</v>
       </c>
       <c r="D45" s="1"/>
-      <c r="E45" s="9"/>
+      <c r="E45" s="5"/>
       <c r="F45" s="1" t="s">
         <v>49</v>
       </c>
@@ -1314,7 +1320,7 @@
         <v>37</v>
       </c>
       <c r="D46" s="1"/>
-      <c r="E46" s="9"/>
+      <c r="E46" s="5"/>
       <c r="F46" s="1" t="s">
         <v>50</v>
       </c>
@@ -1327,7 +1333,7 @@
         <v>38</v>
       </c>
       <c r="D47" s="1"/>
-      <c r="E47" s="10"/>
+      <c r="E47" s="6"/>
       <c r="F47" s="3" t="s">
         <v>51</v>
       </c>
@@ -1355,7 +1361,7 @@
         <v>40</v>
       </c>
       <c r="D49" s="1"/>
-      <c r="E49" s="9"/>
+      <c r="E49" s="5"/>
       <c r="F49" s="1" t="s">
         <v>54</v>
       </c>
@@ -1368,7 +1374,7 @@
         <v>41</v>
       </c>
       <c r="D50" s="1"/>
-      <c r="E50" s="9"/>
+      <c r="E50" s="5"/>
       <c r="F50" s="1" t="s">
         <v>55</v>
       </c>
@@ -1381,7 +1387,7 @@
         <v>42</v>
       </c>
       <c r="D51" s="1"/>
-      <c r="E51" s="10"/>
+      <c r="E51" s="6"/>
       <c r="F51" s="1" t="s">
         <v>56</v>
       </c>
@@ -1409,7 +1415,7 @@
         <v>44</v>
       </c>
       <c r="D53" s="1"/>
-      <c r="E53" s="5"/>
+      <c r="E53" s="10"/>
       <c r="F53" s="1" t="s">
         <v>59</v>
       </c>
@@ -1422,7 +1428,7 @@
         <v>45</v>
       </c>
       <c r="D54" s="1"/>
-      <c r="E54" s="5"/>
+      <c r="E54" s="10"/>
       <c r="F54" s="1" t="s">
         <v>61</v>
       </c>
@@ -1435,7 +1441,7 @@
         <v>46</v>
       </c>
       <c r="D55" s="1"/>
-      <c r="E55" s="5"/>
+      <c r="E55" s="10"/>
       <c r="F55" s="3" t="s">
         <v>65</v>
       </c>
@@ -1448,7 +1454,7 @@
         <v>47</v>
       </c>
       <c r="D56" s="1"/>
-      <c r="E56" s="5"/>
+      <c r="E56" s="10"/>
       <c r="F56" s="1" t="s">
         <v>66</v>
       </c>
@@ -1461,7 +1467,7 @@
         <v>48</v>
       </c>
       <c r="D57" s="1"/>
-      <c r="E57" s="5"/>
+      <c r="E57" s="10"/>
       <c r="F57" s="3" t="s">
         <v>62</v>
       </c>
@@ -1474,7 +1480,7 @@
         <v>49</v>
       </c>
       <c r="D58" s="1"/>
-      <c r="E58" s="5"/>
+      <c r="E58" s="10"/>
       <c r="F58" s="1" t="s">
         <v>60</v>
       </c>
@@ -1487,7 +1493,7 @@
         <v>50</v>
       </c>
       <c r="D59" s="1"/>
-      <c r="E59" s="6"/>
+      <c r="E59" s="11"/>
       <c r="F59" s="1" t="s">
         <v>63</v>
       </c>
@@ -1515,7 +1521,7 @@
         <v>52</v>
       </c>
       <c r="D61" s="1"/>
-      <c r="E61" s="9"/>
+      <c r="E61" s="5"/>
       <c r="F61" s="1" t="s">
         <v>68</v>
       </c>
@@ -1528,7 +1534,7 @@
         <v>53</v>
       </c>
       <c r="D62" s="1"/>
-      <c r="E62" s="10"/>
+      <c r="E62" s="6"/>
       <c r="F62" s="2" t="s">
         <v>69</v>
       </c>
@@ -1556,8 +1562,8 @@
         <v>55</v>
       </c>
       <c r="D64" s="1"/>
-      <c r="E64" s="9"/>
-      <c r="F64" s="12" t="s">
+      <c r="E64" s="5"/>
+      <c r="F64" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G64" s="1"/>
@@ -1569,8 +1575,8 @@
         <v>56</v>
       </c>
       <c r="D65" s="1"/>
-      <c r="E65" s="10"/>
-      <c r="F65" s="13" t="s">
+      <c r="E65" s="6"/>
+      <c r="F65" s="1" t="s">
         <v>73</v>
       </c>
       <c r="G65" s="1"/>
@@ -1597,7 +1603,7 @@
         <v>58</v>
       </c>
       <c r="D67" s="1"/>
-      <c r="E67" s="9"/>
+      <c r="E67" s="5"/>
       <c r="F67" s="1" t="s">
         <v>76</v>
       </c>
@@ -1610,7 +1616,7 @@
         <v>59</v>
       </c>
       <c r="D68" s="1"/>
-      <c r="E68" s="10"/>
+      <c r="E68" s="6"/>
       <c r="F68" s="1" t="s">
         <v>77</v>
       </c>
